--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Tillåtna värden för fältet typeOfDiagnosis i GetDiagnosis.</t>
+    <t>Tillåtna värden för fältet typeOfDiagnosis i GetDiagnosis: HD (huvuddiagnos) och BY (bidiagnos) från kv_diagnostyp.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,7 +108,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://fhir.inera.se/clinicalprocess-healthcond-description/CodeSystem/diagnosistype-cs</t>
+    <t>https://terminologitjansten.inera.se/inera-kodverksforvaltning/kodverk/kv_diagnostyp</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T11:47:48+00:00</t>
+    <t>2026-10-06T07:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-diagnosistype-vs.xlsx
+++ b/ValueSet-diagnosistype-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
